--- a/assets/exports/wholesale-market-shares.xlsx
+++ b/assets/exports/wholesale-market-shares.xlsx
@@ -550,7 +550,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Wholesale market shares</t>
+          <t>Grossistandeler</t>
         </is>
       </c>
     </row>

--- a/assets/exports/wholesale-market-shares.xlsx
+++ b/assets/exports/wholesale-market-shares.xlsx
@@ -659,13 +659,13 @@
         <v>0.5036846465501904</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.4761081007489886</v>
+        <v>0.4803994363914779</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.4659827248356685</v>
+        <v>0.4697615747881192</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.4631837435484176</v>
+        <v>0.4669868847509004</v>
       </c>
       <c r="H5" s="11" t="n">
         <v>3008895</v>
@@ -677,13 +677,13 @@
         <v>3032035</v>
       </c>
       <c r="K5" s="12" t="n">
-        <v>2881610</v>
+        <v>2907583</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>2841510</v>
+        <v>2864553</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>2834779</v>
+        <v>2858055</v>
       </c>
     </row>
     <row r="6">
@@ -702,13 +702,13 @@
         <v>0.3705110994568009</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.3781528669155585</v>
+        <v>0.3738615312730693</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.3735511989644937</v>
+        <v>0.369772349012043</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>0.3654574259289396</v>
+        <v>0.3616542847264569</v>
       </c>
       <c r="H6" s="11" t="n">
         <v>2186759</v>
@@ -720,13 +720,13 @@
         <v>2230369</v>
       </c>
       <c r="K6" s="12" t="n">
-        <v>2288743</v>
+        <v>2262770</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>2277873</v>
+        <v>2254830</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>2236674</v>
+        <v>2213398</v>
       </c>
     </row>
     <row r="7">
